--- a/research/traditional_assets/database/data/vietnam/vietnam_electronics_consumer_office.xlsx
+++ b/research/traditional_assets/database/data/vietnam/vietnam_electronics_consumer_office.xlsx
@@ -636,13 +636,13 @@
         <v>0.266</v>
       </c>
       <c r="V2">
-        <v>0.04440734557595993</v>
+        <v>0.03906020558002937</v>
       </c>
       <c r="X2">
-        <v>0.104839020237625</v>
+        <v>0.1610473994822011</v>
       </c>
       <c r="AB2">
-        <v>0.104839020237625</v>
+        <v>0.1610473994822011</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -663,7 +663,7 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>-0.04647099930118798</v>
+        <v>-0.0406479217603912</v>
       </c>
       <c r="AK2">
         <v>-0.02902662592754256</v>
@@ -746,13 +746,13 @@
         <v>0.266</v>
       </c>
       <c r="V3">
-        <v>0.04440734557595993</v>
+        <v>0.03906020558002937</v>
       </c>
       <c r="X3">
-        <v>0.104839020237625</v>
+        <v>0.1610473994822011</v>
       </c>
       <c r="AB3">
-        <v>0.104839020237625</v>
+        <v>0.1610473994822011</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -773,7 +773,7 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.04647099930118798</v>
+        <v>-0.0406479217603912</v>
       </c>
       <c r="AK3">
         <v>-0.02902662592754256</v>

--- a/research/traditional_assets/database/data/vietnam/vietnam_electronics_consumer_office.xlsx
+++ b/research/traditional_assets/database/data/vietnam/vietnam_electronics_consumer_office.xlsx
@@ -636,13 +636,13 @@
         <v>0.266</v>
       </c>
       <c r="V2">
-        <v>0.03906020558002937</v>
+        <v>0.04202211690363349</v>
       </c>
       <c r="X2">
-        <v>0.1610473994822011</v>
+        <v>0.1379767237311277</v>
       </c>
       <c r="AB2">
-        <v>0.1610473994822011</v>
+        <v>0.1379767237311277</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -663,7 +663,7 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>-0.0406479217603912</v>
+        <v>-0.04386543535620053</v>
       </c>
       <c r="AK2">
         <v>-0.02902662592754256</v>
@@ -746,13 +746,13 @@
         <v>0.266</v>
       </c>
       <c r="V3">
-        <v>0.03906020558002937</v>
+        <v>0.04202211690363349</v>
       </c>
       <c r="X3">
-        <v>0.1610473994822011</v>
+        <v>0.1379767237311277</v>
       </c>
       <c r="AB3">
-        <v>0.1610473994822011</v>
+        <v>0.1379767237311277</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -773,7 +773,7 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.0406479217603912</v>
+        <v>-0.04386543535620053</v>
       </c>
       <c r="AK3">
         <v>-0.02902662592754256</v>
